--- a/src/main/vue/src/assets/excel/DOI_ReportTemplate2.xlsx
+++ b/src/main/vue/src/assets/excel/DOI_ReportTemplate2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\dwisCOST\src\main\vue\src\assets\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64844D4-633E-4170-B536-1A61D1370C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C178300F-B8F2-4242-A42B-EF47B057B456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35175" yWindow="4020" windowWidth="22155" windowHeight="11355" xr2:uid="{ADB685F9-3B90-4289-8BC8-D84767B26EA3}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{ADB685F9-3B90-4289-8BC8-D84767B26EA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -1277,7 +1277,7 @@
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="4.3984375" customWidth="1"/>
-    <col min="2" max="2" width="35.5" customWidth="1"/>
+    <col min="2" max="2" width="46.69921875" customWidth="1"/>
     <col min="3" max="15" width="20.19921875" customWidth="1"/>
   </cols>
   <sheetData>
